--- a/SCE_skewness_lt.xlsx
+++ b/SCE_skewness_lt.xlsx
@@ -75,7 +75,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E149"/>
+  <dimension ref="A1:E157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -148,13 +148,13 @@
         <v>0.78268885612487793</v>
       </c>
       <c r="C7" s="2">
-        <v>0.45126700401306152</v>
+        <v>0.4529096782207489</v>
       </c>
       <c r="D7" s="2">
         <v>0.2218918651342392</v>
       </c>
       <c r="E7" s="2">
-        <v>-0.0079543497413396835</v>
+        <v>-0.0087517742067575455</v>
       </c>
     </row>
     <row r="8">
@@ -165,13 +165,13 @@
         <v>0.15686279535293579</v>
       </c>
       <c r="C8" s="2">
-        <v>-0.091899752616882324</v>
+        <v>-0.098458535969257355</v>
       </c>
       <c r="D8" s="2">
         <v>0.17378032207489014</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.044374551624059677</v>
+        <v>-0.044307950884103775</v>
       </c>
     </row>
     <row r="9">
@@ -182,13 +182,13 @@
         <v>0.18897454440593719</v>
       </c>
       <c r="C9" s="2">
-        <v>-0.0043612243607640266</v>
+        <v>-0.0030287723056972027</v>
       </c>
       <c r="D9" s="2">
         <v>0.088357903063297272</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.1810469776391983</v>
+        <v>-0.18091198801994324</v>
       </c>
     </row>
     <row r="10">
@@ -199,13 +199,13 @@
         <v>-0.74811232089996338</v>
       </c>
       <c r="C10" s="2">
-        <v>-0.98122125864028931</v>
+        <v>-0.98712837696075439</v>
       </c>
       <c r="D10" s="2">
         <v>-0.00062036514282226562</v>
       </c>
       <c r="E10" s="2">
-        <v>-0.2882845401763916</v>
+        <v>-0.28752484917640686</v>
       </c>
     </row>
     <row r="11">
@@ -216,13 +216,13 @@
         <v>0.72904545068740845</v>
       </c>
       <c r="C11" s="2">
-        <v>0.58644348382949829</v>
+        <v>0.59194713830947876</v>
       </c>
       <c r="D11" s="2">
         <v>-0.034015536308288574</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.31021249294281006</v>
+        <v>-0.3084740936756134</v>
       </c>
     </row>
     <row r="12">
@@ -233,13 +233,13 @@
         <v>-0.066777423024177551</v>
       </c>
       <c r="C12" s="2">
-        <v>-0.2264755517244339</v>
+        <v>-0.22208882868289948</v>
       </c>
       <c r="D12" s="2">
         <v>-0.14139465987682343</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.414947509765625</v>
+        <v>-0.41369044780731201</v>
       </c>
     </row>
     <row r="13">
@@ -250,13 +250,13 @@
         <v>-0.42417660355567932</v>
       </c>
       <c r="C13" s="2">
-        <v>-1.0010815858840942</v>
+        <v>-1.0005362033843994</v>
       </c>
       <c r="D13" s="2">
         <v>-0.26401475071907043</v>
       </c>
       <c r="E13" s="2">
-        <v>-0.53513509035110474</v>
+        <v>-0.5327984094619751</v>
       </c>
     </row>
     <row r="14">
@@ -267,13 +267,13 @@
         <v>-0.62346822023391724</v>
       </c>
       <c r="C14" s="2">
-        <v>-1.0389473438262939</v>
+        <v>-1.0338147878646851</v>
       </c>
       <c r="D14" s="2">
         <v>-0.38697963953018188</v>
       </c>
       <c r="E14" s="2">
-        <v>-0.66375309228897095</v>
+        <v>-0.66128331422805786</v>
       </c>
     </row>
     <row r="15">
@@ -284,13 +284,13 @@
         <v>-0.30117690563201904</v>
       </c>
       <c r="C15" s="2">
-        <v>-0.48563608527183533</v>
+        <v>-0.47606807947158813</v>
       </c>
       <c r="D15" s="2">
         <v>-0.42463892698287964</v>
       </c>
       <c r="E15" s="2">
-        <v>-0.6933942437171936</v>
+        <v>-0.69040423631668091</v>
       </c>
     </row>
     <row r="16">
@@ -301,13 +301,13 @@
         <v>-0.18372327089309692</v>
       </c>
       <c r="C16" s="2">
-        <v>-0.49134838581085205</v>
+        <v>-0.49403756856918335</v>
       </c>
       <c r="D16" s="2">
         <v>-0.53174930810928345</v>
       </c>
       <c r="E16" s="2">
-        <v>-0.80179512500762939</v>
+        <v>-0.79960811138153076</v>
       </c>
     </row>
     <row r="17">
@@ -318,13 +318,13 @@
         <v>-0.94671797752380371</v>
       </c>
       <c r="C17" s="2">
-        <v>-1.1735876798629761</v>
+        <v>-1.1704301834106445</v>
       </c>
       <c r="D17" s="2">
         <v>-0.53817242383956909</v>
       </c>
       <c r="E17" s="2">
-        <v>-0.83389961719512939</v>
+        <v>-0.83157932758331299</v>
       </c>
     </row>
     <row r="18">
@@ -335,13 +335,13 @@
         <v>-0.9177095890045166</v>
       </c>
       <c r="C18" s="2">
-        <v>-1.1619235277175903</v>
+        <v>-1.1593931913375854</v>
       </c>
       <c r="D18" s="2">
         <v>-0.4437943696975708</v>
       </c>
       <c r="E18" s="2">
-        <v>-0.68923324346542358</v>
+        <v>-0.6871572732925415</v>
       </c>
     </row>
     <row r="19">
@@ -352,13 +352,13 @@
         <v>-1.0870456695556641</v>
       </c>
       <c r="C19" s="2">
-        <v>-1.247991681098938</v>
+        <v>-1.2492161989212036</v>
       </c>
       <c r="D19" s="2">
         <v>-0.37045866250991821</v>
       </c>
       <c r="E19" s="2">
-        <v>-0.61247944831848145</v>
+        <v>-0.61081808805465698</v>
       </c>
     </row>
     <row r="20">
@@ -369,13 +369,13 @@
         <v>-0.23494830727577209</v>
       </c>
       <c r="C20" s="2">
-        <v>-0.38916414976119995</v>
+        <v>-0.39088773727416992</v>
       </c>
       <c r="D20" s="2">
         <v>-0.3531804084777832</v>
       </c>
       <c r="E20" s="2">
-        <v>-0.59967517852783203</v>
+        <v>-0.5986444354057312</v>
       </c>
     </row>
     <row r="21">
@@ -386,13 +386,13 @@
         <v>-0.12458525598049164</v>
       </c>
       <c r="C21" s="2">
-        <v>-0.51541614532470703</v>
+        <v>-0.50982975959777832</v>
       </c>
       <c r="D21" s="2">
         <v>-0.40877041220664978</v>
       </c>
       <c r="E21" s="2">
-        <v>-0.64511692523956299</v>
+        <v>-0.64364558458328247</v>
       </c>
     </row>
     <row r="22">
@@ -403,13 +403,13 @@
         <v>0.4252258837223053</v>
       </c>
       <c r="C22" s="2">
-        <v>0.30091604590415955</v>
+        <v>0.29926180839538574</v>
       </c>
       <c r="D22" s="2">
         <v>-0.26891836524009705</v>
       </c>
       <c r="E22" s="2">
-        <v>-0.49097248911857605</v>
+        <v>-0.49119040369987488</v>
       </c>
     </row>
     <row r="23">
@@ -420,13 +420,13 @@
         <v>0.036553103476762772</v>
       </c>
       <c r="C23" s="2">
-        <v>-0.34816339612007141</v>
+        <v>-0.34676182270050049</v>
       </c>
       <c r="D23" s="2">
         <v>-0.2529655396938324</v>
       </c>
       <c r="E23" s="2">
-        <v>-0.47600138187408447</v>
+        <v>-0.47553080320358276</v>
       </c>
     </row>
     <row r="24">
@@ -437,13 +437,13 @@
         <v>-0.14567272365093231</v>
       </c>
       <c r="C24" s="2">
-        <v>-0.37039762735366821</v>
+        <v>-0.36650544404983521</v>
       </c>
       <c r="D24" s="2">
         <v>-0.16137813031673431</v>
       </c>
       <c r="E24" s="2">
-        <v>-0.39726114273071289</v>
+        <v>-0.39589563012123108</v>
       </c>
     </row>
     <row r="25">
@@ -454,13 +454,13 @@
         <v>-0.68403315544128418</v>
       </c>
       <c r="C25" s="2">
-        <v>-0.90032428503036499</v>
+        <v>-0.8990476131439209</v>
       </c>
       <c r="D25" s="2">
         <v>-0.17549227178096771</v>
       </c>
       <c r="E25" s="2">
-        <v>-0.42922618985176086</v>
+        <v>-0.42794111371040344</v>
       </c>
     </row>
     <row r="26">
@@ -471,13 +471,13 @@
         <v>0.31195035576820374</v>
       </c>
       <c r="C26" s="2">
-        <v>0.21371228992938995</v>
+        <v>0.20166629552841187</v>
       </c>
       <c r="D26" s="2">
         <v>-0.14565975964069366</v>
       </c>
       <c r="E26" s="2">
-        <v>-0.38854575157165527</v>
+        <v>-0.38726583123207092</v>
       </c>
     </row>
     <row r="27">
@@ -488,13 +488,13 @@
         <v>-0.77413409948348999</v>
       </c>
       <c r="C27" s="2">
-        <v>-1.0271834135055542</v>
+        <v>-1.0184566974639893</v>
       </c>
       <c r="D27" s="2">
         <v>-0.20474058389663696</v>
       </c>
       <c r="E27" s="2">
-        <v>-0.47709783911705017</v>
+        <v>-0.47461873292922974</v>
       </c>
     </row>
     <row r="28">
@@ -505,13 +505,13 @@
         <v>-0.26275897026062012</v>
       </c>
       <c r="C28" s="2">
-        <v>-0.53932958841323853</v>
+        <v>-0.53249973058700562</v>
       </c>
       <c r="D28" s="2">
         <v>-0.19938744604587555</v>
       </c>
       <c r="E28" s="2">
-        <v>-0.45014014840126038</v>
+        <v>-0.44694536924362183</v>
       </c>
     </row>
     <row r="29">
@@ -522,13 +522,13 @@
         <v>-0.36197552084922791</v>
       </c>
       <c r="C29" s="2">
-        <v>-0.67684966325759888</v>
+        <v>-0.67929702997207642</v>
       </c>
       <c r="D29" s="2">
         <v>-0.30479460954666138</v>
       </c>
       <c r="E29" s="2">
-        <v>-0.56580287218093872</v>
+        <v>-0.56291866302490234</v>
       </c>
     </row>
     <row r="30">
@@ -539,13 +539,13 @@
         <v>0.1439073234796524</v>
       </c>
       <c r="C30" s="2">
-        <v>-0.14929209649562836</v>
+        <v>-0.14375226199626923</v>
       </c>
       <c r="D30" s="2">
         <v>-0.1995169073343277</v>
       </c>
       <c r="E30" s="2">
-        <v>-0.47083809971809387</v>
+        <v>-0.46722143888473511</v>
       </c>
     </row>
     <row r="31">
@@ -556,13 +556,13 @@
         <v>-0.10650155693292618</v>
       </c>
       <c r="C31" s="2">
-        <v>-0.49605280160903931</v>
+        <v>-0.48691442608833313</v>
       </c>
       <c r="D31" s="2">
         <v>-0.22797907888889313</v>
       </c>
       <c r="E31" s="2">
-        <v>-0.51001983880996704</v>
+        <v>-0.50524270534515381</v>
       </c>
     </row>
     <row r="32">
@@ -573,13 +573,13 @@
         <v>0.084731347858905792</v>
       </c>
       <c r="C32" s="2">
-        <v>-0.10554424673318863</v>
+        <v>-0.097701288759708405</v>
       </c>
       <c r="D32" s="2">
         <v>-0.18691584467887878</v>
       </c>
       <c r="E32" s="2">
-        <v>-0.46470871567726135</v>
+        <v>-0.45905852317810059</v>
       </c>
     </row>
     <row r="33">
@@ -590,13 +590,13 @@
         <v>-1.0943372249603271</v>
       </c>
       <c r="C33" s="2">
-        <v>-1.4113621711730957</v>
+        <v>-1.4102654457092285</v>
       </c>
       <c r="D33" s="2">
         <v>-0.094962827861309052</v>
       </c>
       <c r="E33" s="2">
-        <v>-0.34936064481735229</v>
+        <v>-0.34296134114265442</v>
       </c>
     </row>
     <row r="34">
@@ -607,13 +607,13 @@
         <v>0.26346617937088013</v>
       </c>
       <c r="C34" s="2">
-        <v>-0.045641202479600906</v>
+        <v>-0.037772286683320999</v>
       </c>
       <c r="D34" s="2">
         <v>-0.057181075215339661</v>
       </c>
       <c r="E34" s="2">
-        <v>-0.29727217555046082</v>
+        <v>-0.29169768095016479</v>
       </c>
     </row>
     <row r="35">
@@ -624,13 +624,13 @@
         <v>0.055790852755308151</v>
       </c>
       <c r="C35" s="2">
-        <v>-0.13892333209514618</v>
+        <v>-0.14052528142929077</v>
       </c>
       <c r="D35" s="2">
         <v>-0.0012686821864917874</v>
       </c>
       <c r="E35" s="2">
-        <v>-0.24080274999141693</v>
+        <v>-0.23693360388278961</v>
       </c>
     </row>
     <row r="36">
@@ -641,13 +641,13 @@
         <v>-0.40456500649452209</v>
       </c>
       <c r="C36" s="2">
-        <v>-0.61938327550888062</v>
+        <v>-0.6027989387512207</v>
       </c>
       <c r="D36" s="2">
         <v>-0.031225046142935753</v>
       </c>
       <c r="E36" s="2">
-        <v>-0.21680641174316406</v>
+        <v>-0.21432919800281525</v>
       </c>
     </row>
     <row r="37">
@@ -658,13 +658,13 @@
         <v>0.56481814384460449</v>
       </c>
       <c r="C37" s="2">
-        <v>0.49880290031433105</v>
+        <v>0.51237499713897705</v>
       </c>
       <c r="D37" s="2">
         <v>-0.050016406923532486</v>
       </c>
       <c r="E37" s="2">
-        <v>-0.2548794150352478</v>
+        <v>-0.25286635756492615</v>
       </c>
     </row>
     <row r="38">
@@ -675,13 +675,13 @@
         <v>-0.02193974144756794</v>
       </c>
       <c r="C38" s="2">
-        <v>-0.20805348455905914</v>
+        <v>-0.21792420744895935</v>
       </c>
       <c r="D38" s="2">
         <v>0.17442938685417175</v>
       </c>
       <c r="E38" s="2">
-        <v>-0.03809085488319397</v>
+        <v>-0.035900212824344635</v>
       </c>
     </row>
     <row r="39">
@@ -692,13 +692,13 @@
         <v>0.64711886644363403</v>
       </c>
       <c r="C39" s="2">
-        <v>0.35893282294273376</v>
+        <v>0.34912446141242981</v>
       </c>
       <c r="D39" s="2">
         <v>0.10004933923482895</v>
       </c>
       <c r="E39" s="2">
-        <v>-0.10992106795310974</v>
+        <v>-0.10806173831224442</v>
       </c>
     </row>
     <row r="40">
@@ -709,13 +709,13 @@
         <v>-0.37610882520675659</v>
       </c>
       <c r="C40" s="2">
-        <v>-0.28008571267127991</v>
+        <v>-0.28347480297088623</v>
       </c>
       <c r="D40" s="2">
         <v>0.14019784331321716</v>
       </c>
       <c r="E40" s="2">
-        <v>-0.10207262635231018</v>
+        <v>-0.098895885050296783</v>
       </c>
     </row>
     <row r="41">
@@ -726,13 +726,13 @@
         <v>-0.084390901029109955</v>
       </c>
       <c r="C41" s="2">
-        <v>-0.44820123910903931</v>
+        <v>-0.44453573226928711</v>
       </c>
       <c r="D41" s="2">
         <v>0.22562626004219055</v>
       </c>
       <c r="E41" s="2">
-        <v>-0.015899337828159332</v>
+        <v>-0.014517013914883137</v>
       </c>
     </row>
     <row r="42">
@@ -743,13 +743,13 @@
         <v>0.9256749153137207</v>
       </c>
       <c r="C42" s="2">
-        <v>0.53973484039306641</v>
+        <v>0.54242986440658569</v>
       </c>
       <c r="D42" s="2">
         <v>0.17017181217670441</v>
       </c>
       <c r="E42" s="2">
-        <v>-0.091625243425369263</v>
+        <v>-0.091007351875305176</v>
       </c>
     </row>
     <row r="43">
@@ -760,13 +760,13 @@
         <v>-0.40595424175262451</v>
       </c>
       <c r="C43" s="2">
-        <v>-0.69211310148239136</v>
+        <v>-0.68722599744796753</v>
       </c>
       <c r="D43" s="2">
         <v>0.1400931179523468</v>
       </c>
       <c r="E43" s="2">
-        <v>-0.14145204424858093</v>
+        <v>-0.13859562575817108</v>
       </c>
     </row>
     <row r="44">
@@ -777,13 +777,13 @@
         <v>0.4171273410320282</v>
       </c>
       <c r="C44" s="2">
-        <v>-0.068287357687950134</v>
+        <v>-0.058032583445310593</v>
       </c>
       <c r="D44" s="2">
         <v>0.015988118946552277</v>
       </c>
       <c r="E44" s="2">
-        <v>-0.24894708395004272</v>
+        <v>-0.24508948624134064</v>
       </c>
     </row>
     <row r="45">
@@ -794,13 +794,13 @@
         <v>0.3642907440662384</v>
       </c>
       <c r="C45" s="2">
-        <v>0.15617629885673523</v>
+        <v>0.1566108763217926</v>
       </c>
       <c r="D45" s="2">
         <v>0.053154107183218002</v>
       </c>
       <c r="E45" s="2">
-        <v>-0.25684124231338501</v>
+        <v>-0.25245100259780884</v>
       </c>
     </row>
     <row r="46">
@@ -811,13 +811,13 @@
         <v>0.065728098154067993</v>
       </c>
       <c r="C46" s="2">
-        <v>-0.18273027241230011</v>
+        <v>-0.17603805661201477</v>
       </c>
       <c r="D46" s="2">
         <v>0.0014584200689569116</v>
       </c>
       <c r="E46" s="2">
-        <v>-0.28225982189178467</v>
+        <v>-0.27758240699768066</v>
       </c>
     </row>
     <row r="47">
@@ -828,13 +828,13 @@
         <v>-0.29264798760414124</v>
       </c>
       <c r="C47" s="2">
-        <v>-0.65649467706680298</v>
+        <v>-0.64621865749359131</v>
       </c>
       <c r="D47" s="2">
         <v>-0.19763895869255066</v>
       </c>
       <c r="E47" s="2">
-        <v>-0.46872112154960632</v>
+        <v>-0.46415862441062927</v>
       </c>
     </row>
     <row r="48">
@@ -845,13 +845,13 @@
         <v>-0.46982607245445251</v>
       </c>
       <c r="C48" s="2">
-        <v>-0.60852247476577759</v>
+        <v>-0.60932022333145142</v>
       </c>
       <c r="D48" s="2">
         <v>-0.20262032747268677</v>
       </c>
       <c r="E48" s="2">
-        <v>-0.46353951096534729</v>
+        <v>-0.45947962999343872</v>
       </c>
     </row>
     <row r="49">
@@ -862,13 +862,13 @@
         <v>-0.041614916175603867</v>
       </c>
       <c r="C49" s="2">
-        <v>-0.35113322734832764</v>
+        <v>-0.34972846508026123</v>
       </c>
       <c r="D49" s="2">
         <v>-0.29348841309547424</v>
       </c>
       <c r="E49" s="2">
-        <v>-0.54592907428741455</v>
+        <v>-0.54222476482391357</v>
       </c>
     </row>
     <row r="50">
@@ -879,13 +879,13 @@
         <v>-0.549652099609375</v>
       </c>
       <c r="C50" s="2">
-        <v>-0.67696845531463623</v>
+        <v>-0.67071831226348877</v>
       </c>
       <c r="D50" s="2">
         <v>-0.29693049192428589</v>
       </c>
       <c r="E50" s="2">
-        <v>-0.54172718524932861</v>
+        <v>-0.53818744421005249</v>
       </c>
     </row>
     <row r="51">
@@ -896,13 +896,13 @@
         <v>-0.86620146036148071</v>
       </c>
       <c r="C51" s="2">
-        <v>-1.1384168863296509</v>
+        <v>-1.1367563009262085</v>
       </c>
       <c r="D51" s="2">
         <v>-0.33952206373214722</v>
       </c>
       <c r="E51" s="2">
-        <v>-0.59146428108215332</v>
+        <v>-0.58678346872329712</v>
       </c>
     </row>
     <row r="52">
@@ -913,13 +913,13 @@
         <v>-0.45078656077384949</v>
       </c>
       <c r="C52" s="2">
-        <v>-0.64547854661941528</v>
+        <v>-0.64511483907699585</v>
       </c>
       <c r="D52" s="2">
         <v>-0.29222095012664795</v>
       </c>
       <c r="E52" s="2">
-        <v>-0.52819555997848511</v>
+        <v>-0.52443420886993408</v>
       </c>
     </row>
     <row r="53">
@@ -930,13 +930,13 @@
         <v>-0.40068542957305908</v>
       </c>
       <c r="C53" s="2">
-        <v>-0.80979365110397339</v>
+        <v>-0.80273896455764771</v>
       </c>
       <c r="D53" s="2">
         <v>-0.19391623139381409</v>
       </c>
       <c r="E53" s="2">
-        <v>-0.45654883980751038</v>
+        <v>-0.45086115598678589</v>
       </c>
     </row>
     <row r="54">
@@ -947,13 +947,13 @@
         <v>0.33331206440925598</v>
       </c>
       <c r="C54" s="2">
-        <v>0.19399358332157135</v>
+        <v>0.19294668734073639</v>
       </c>
       <c r="D54" s="2">
         <v>-0.29071322083473206</v>
       </c>
       <c r="E54" s="2">
-        <v>-0.55319094657897949</v>
+        <v>-0.54724293947219849</v>
       </c>
     </row>
     <row r="55">
@@ -964,13 +964,13 @@
         <v>-0.31759613752365112</v>
       </c>
       <c r="C55" s="2">
-        <v>-0.63036423921585083</v>
+        <v>-0.61340194940567017</v>
       </c>
       <c r="D55" s="2">
         <v>-0.22996386885643005</v>
       </c>
       <c r="E55" s="2">
-        <v>-0.49992427229881287</v>
+        <v>-0.49410971999168396</v>
       </c>
     </row>
     <row r="56">
@@ -981,13 +981,13 @@
         <v>0.13306212425231934</v>
       </c>
       <c r="C56" s="2">
-        <v>-0.087076209485530853</v>
+        <v>-0.085075333714485168</v>
       </c>
       <c r="D56" s="2">
         <v>-0.1662299782037735</v>
       </c>
       <c r="E56" s="2">
-        <v>-0.45008304715156555</v>
+        <v>-0.44354522228240967</v>
       </c>
     </row>
     <row r="57">
@@ -998,13 +998,13 @@
         <v>0.41491639614105225</v>
       </c>
       <c r="C57" s="2">
-        <v>0.036298055201768875</v>
+        <v>0.05283697322010994</v>
       </c>
       <c r="D57" s="2">
         <v>-0.13520701229572296</v>
       </c>
       <c r="E57" s="2">
-        <v>-0.43848448991775513</v>
+        <v>-0.42988881468772888</v>
       </c>
     </row>
     <row r="58">
@@ -1015,13 +1015,13 @@
         <v>-0.91278797388076782</v>
       </c>
       <c r="C58" s="2">
-        <v>-1.2209123373031616</v>
+        <v>-1.2171645164489746</v>
       </c>
       <c r="D58" s="2">
         <v>-0.09638301283121109</v>
       </c>
       <c r="E58" s="2">
-        <v>-0.38815757632255554</v>
+        <v>-0.38068005442619324</v>
       </c>
     </row>
     <row r="59">
@@ -1032,13 +1032,13 @@
         <v>-0.0029078770894557238</v>
       </c>
       <c r="C59" s="2">
-        <v>-0.19756826758384705</v>
+        <v>-0.19251923263072968</v>
       </c>
       <c r="D59" s="2">
         <v>-0.23010538518428802</v>
       </c>
       <c r="E59" s="2">
-        <v>-0.54527449607849121</v>
+        <v>-0.53753244876861572</v>
       </c>
     </row>
     <row r="60">
@@ -1049,13 +1049,13 @@
         <v>-0.29259639978408813</v>
       </c>
       <c r="C60" s="2">
-        <v>-0.68984586000442505</v>
+        <v>-0.68167591094970703</v>
       </c>
       <c r="D60" s="2">
         <v>-0.25478518009185791</v>
       </c>
       <c r="E60" s="2">
-        <v>-0.56728851795196533</v>
+        <v>-0.56216925382614136</v>
       </c>
     </row>
     <row r="61">
@@ -1066,13 +1066,13 @@
         <v>-0.17157986760139465</v>
       </c>
       <c r="C61" s="2">
-        <v>-0.5410914421081543</v>
+        <v>-0.52220708131790161</v>
       </c>
       <c r="D61" s="2">
         <v>-0.33349129557609558</v>
       </c>
       <c r="E61" s="2">
-        <v>-0.64581072330474854</v>
+        <v>-0.64093643426895142</v>
       </c>
     </row>
     <row r="62">
@@ -1083,13 +1083,13 @@
         <v>-0.051269475370645523</v>
       </c>
       <c r="C62" s="2">
-        <v>-0.35685136914253235</v>
+        <v>-0.35986000299453735</v>
       </c>
       <c r="D62" s="2">
         <v>-0.34285661578178406</v>
       </c>
       <c r="E62" s="2">
-        <v>-0.63862341642379761</v>
+        <v>-0.63498926162719727</v>
       </c>
     </row>
     <row r="63">
@@ -1100,13 +1100,13 @@
         <v>-0.87018924951553345</v>
       </c>
       <c r="C63" s="2">
-        <v>-1.2200586795806885</v>
+        <v>-1.2187250852584839</v>
       </c>
       <c r="D63" s="2">
         <v>-0.29188269376754761</v>
       </c>
       <c r="E63" s="2">
-        <v>-0.58535164594650269</v>
+        <v>-0.58129888772964478</v>
       </c>
     </row>
     <row r="64">
@@ -1117,13 +1117,13 @@
         <v>-0.53971433639526367</v>
       </c>
       <c r="C64" s="2">
-        <v>-0.8284907341003418</v>
+        <v>-0.83513319492340088</v>
       </c>
       <c r="D64" s="2">
         <v>-0.30785155296325684</v>
       </c>
       <c r="E64" s="2">
-        <v>-0.60547620058059692</v>
+        <v>-0.60031694173812866</v>
       </c>
     </row>
     <row r="65">
@@ -1134,13 +1134,13 @@
         <v>-0.57529282569885254</v>
       </c>
       <c r="C65" s="2">
-        <v>-0.79377579689025879</v>
+        <v>-0.7939799427986145</v>
       </c>
       <c r="D65" s="2">
         <v>-0.15254397690296173</v>
       </c>
       <c r="E65" s="2">
-        <v>-0.42581900954246521</v>
+        <v>-0.42195197939872742</v>
       </c>
     </row>
     <row r="66">
@@ -1151,13 +1151,13 @@
         <v>0.33062833547592163</v>
       </c>
       <c r="C66" s="2">
-        <v>0.10098367929458618</v>
+        <v>0.10636140406131744</v>
       </c>
       <c r="D66" s="2">
         <v>-0.16346608102321625</v>
       </c>
       <c r="E66" s="2">
-        <v>-0.42062550783157349</v>
+        <v>-0.41879156231880188</v>
       </c>
     </row>
     <row r="67">
@@ -1168,13 +1168,13 @@
         <v>-0.45402267575263977</v>
       </c>
       <c r="C67" s="2">
-        <v>-0.74146640300750732</v>
+        <v>-0.73395109176635742</v>
       </c>
       <c r="D67" s="2">
         <v>-0.29474163055419922</v>
       </c>
       <c r="E67" s="2">
-        <v>-0.56144893169403076</v>
+        <v>-0.55793958902359009</v>
       </c>
     </row>
     <row r="68">
@@ -1185,13 +1185,13 @@
         <v>-0.14662759006023407</v>
       </c>
       <c r="C68" s="2">
-        <v>-0.37868914008140564</v>
+        <v>-0.36368173360824585</v>
       </c>
       <c r="D68" s="2">
         <v>-0.093412399291992188</v>
       </c>
       <c r="E68" s="2">
-        <v>-0.35192969441413879</v>
+        <v>-0.34769821166992188</v>
       </c>
     </row>
     <row r="69">
@@ -1202,13 +1202,13 @@
         <v>1.1051719188690186</v>
       </c>
       <c r="C69" s="2">
-        <v>0.92706882953643799</v>
+        <v>0.92360883951187134</v>
       </c>
       <c r="D69" s="2">
         <v>-0.12076326459646225</v>
       </c>
       <c r="E69" s="2">
-        <v>-0.38512557744979858</v>
+        <v>-0.37803009152412415</v>
       </c>
     </row>
     <row r="70">
@@ -1219,13 +1219,13 @@
         <v>-0.26987883448600769</v>
       </c>
       <c r="C70" s="2">
-        <v>-0.49435004591941833</v>
+        <v>-0.493763267993927</v>
       </c>
       <c r="D70" s="2">
         <v>-0.17930825054645538</v>
       </c>
       <c r="E70" s="2">
-        <v>-0.439809650182724</v>
+        <v>-0.43236845731735229</v>
       </c>
     </row>
     <row r="71">
@@ -1236,13 +1236,13 @@
         <v>-1.2327494621276855</v>
       </c>
       <c r="C71" s="2">
-        <v>-1.6242619752883911</v>
+        <v>-1.6121920347213745</v>
       </c>
       <c r="D71" s="2">
         <v>-0.27727213501930237</v>
       </c>
       <c r="E71" s="2">
-        <v>-0.53502142429351807</v>
+        <v>-0.52871936559677124</v>
       </c>
     </row>
     <row r="72">
@@ -1253,13 +1253,13 @@
         <v>0.94177389144897461</v>
       </c>
       <c r="C72" s="2">
-        <v>0.66561430692672729</v>
+        <v>0.67344707250595093</v>
       </c>
       <c r="D72" s="2">
         <v>-0.33878284692764282</v>
       </c>
       <c r="E72" s="2">
-        <v>-0.5932776927947998</v>
+        <v>-0.58761847019195557</v>
       </c>
     </row>
     <row r="73">
@@ -1270,13 +1270,13 @@
         <v>-0.78587216138839722</v>
       </c>
       <c r="C73" s="2">
-        <v>-1.1272536516189575</v>
+        <v>-1.1081200838088989</v>
       </c>
       <c r="D73" s="2">
         <v>-0.29063433408737183</v>
       </c>
       <c r="E73" s="2">
-        <v>-0.54054218530654907</v>
+        <v>-0.53611230850219727</v>
       </c>
     </row>
     <row r="74">
@@ -1287,13 +1287,13 @@
         <v>-1.1021976470947266</v>
       </c>
       <c r="C74" s="2">
-        <v>-1.2859324216842651</v>
+        <v>-1.2830252647399902</v>
       </c>
       <c r="D74" s="2">
         <v>-0.41044247150421143</v>
       </c>
       <c r="E74" s="2">
-        <v>-0.66071504354476929</v>
+        <v>-0.65537172555923462</v>
       </c>
     </row>
     <row r="75">
@@ -1304,13 +1304,13 @@
         <v>-0.55104660987854004</v>
       </c>
       <c r="C75" s="2">
-        <v>-0.75592207908630371</v>
+        <v>-0.76079672574996948</v>
       </c>
       <c r="D75" s="2">
         <v>-0.36674642562866211</v>
       </c>
       <c r="E75" s="2">
-        <v>-0.61823123693466187</v>
+        <v>-0.61284947395324707</v>
       </c>
     </row>
     <row r="76">
@@ -1321,13 +1321,13 @@
         <v>-1.0076190233230591</v>
       </c>
       <c r="C76" s="2">
-        <v>-1.2657729387283325</v>
+        <v>-1.2640429735183716</v>
       </c>
       <c r="D76" s="2">
         <v>-0.17389242351055145</v>
       </c>
       <c r="E76" s="2">
-        <v>-0.40886077284812927</v>
+        <v>-0.40458127856254578</v>
       </c>
     </row>
     <row r="77">
@@ -1338,13 +1338,13 @@
         <v>0.28670898079872131</v>
       </c>
       <c r="C77" s="2">
-        <v>0.095930516719818115</v>
+        <v>0.099873438477516174</v>
       </c>
       <c r="D77" s="2">
         <v>-0.21892324090003967</v>
       </c>
       <c r="E77" s="2">
-        <v>-0.44758880138397217</v>
+        <v>-0.44293206930160522</v>
       </c>
     </row>
     <row r="78">
@@ -1355,13 +1355,13 @@
         <v>0.026898570358753204</v>
       </c>
       <c r="C78" s="2">
-        <v>-0.1544870138168335</v>
+        <v>-0.14972583949565887</v>
       </c>
       <c r="D78" s="2">
         <v>-0.10211180150508881</v>
       </c>
       <c r="E78" s="2">
-        <v>-0.31424561142921448</v>
+        <v>-0.30879268050193787</v>
       </c>
     </row>
     <row r="79">
@@ -1372,13 +1372,13 @@
         <v>0.12338563054800034</v>
       </c>
       <c r="C79" s="2">
-        <v>-0.11199578642845154</v>
+        <v>-0.11106289923191071</v>
       </c>
       <c r="D79" s="2">
         <v>-0.033451300114393234</v>
       </c>
       <c r="E79" s="2">
-        <v>-0.25542673468589783</v>
+        <v>-0.24918206036090851</v>
       </c>
     </row>
     <row r="80">
@@ -1389,13 +1389,13 @@
         <v>0.50293654203414917</v>
       </c>
       <c r="C80" s="2">
-        <v>0.26007220149040222</v>
+        <v>0.26222175359725952</v>
       </c>
       <c r="D80" s="2">
         <v>-0.011834267526865005</v>
       </c>
       <c r="E80" s="2">
-        <v>-0.26108634471893311</v>
+        <v>-0.2530607283115387</v>
       </c>
     </row>
     <row r="81">
@@ -1406,13 +1406,13 @@
         <v>0.53649652004241943</v>
       </c>
       <c r="C81" s="2">
-        <v>0.31706202030181885</v>
+        <v>0.32829010486602783</v>
       </c>
       <c r="D81" s="2">
         <v>0.067942298948764801</v>
       </c>
       <c r="E81" s="2">
-        <v>-0.1852429211139679</v>
+        <v>-0.17517060041427612</v>
       </c>
     </row>
     <row r="82">
@@ -1423,13 +1423,13 @@
         <v>0.26543080806732178</v>
       </c>
       <c r="C82" s="2">
-        <v>0.072835080325603485</v>
+        <v>0.099134251475334167</v>
       </c>
       <c r="D82" s="2">
         <v>0.079213529825210571</v>
       </c>
       <c r="E82" s="2">
-        <v>-0.17539715766906738</v>
+        <v>-0.16544468700885773</v>
       </c>
     </row>
     <row r="83">
@@ -1440,13 +1440,13 @@
         <v>-0.48425310850143433</v>
       </c>
       <c r="C83" s="2">
-        <v>-0.75656253099441528</v>
+        <v>-0.74652969837188721</v>
       </c>
       <c r="D83" s="2">
         <v>-0.035879045724868774</v>
       </c>
       <c r="E83" s="2">
-        <v>-0.30232354998588562</v>
+        <v>-0.29199010133743286</v>
       </c>
     </row>
     <row r="84">
@@ -1457,13 +1457,13 @@
         <v>-0.35649332404136658</v>
       </c>
       <c r="C84" s="2">
-        <v>-0.80685865879058838</v>
+        <v>-0.79570466279983521</v>
       </c>
       <c r="D84" s="2">
         <v>0.021520733833312988</v>
       </c>
       <c r="E84" s="2">
-        <v>-0.23303702473640442</v>
+        <v>-0.22193838655948639</v>
       </c>
     </row>
     <row r="85">
@@ -1474,13 +1474,13 @@
         <v>-0.28962990641593933</v>
       </c>
       <c r="C85" s="2">
-        <v>-0.58318209648132324</v>
+        <v>-0.56303179264068604</v>
       </c>
       <c r="D85" s="2">
         <v>-0.077597707509994507</v>
       </c>
       <c r="E85" s="2">
-        <v>-0.33648079633712769</v>
+        <v>-0.32528191804885864</v>
       </c>
     </row>
     <row r="86">
@@ -1491,13 +1491,13 @@
         <v>0.38815003633499146</v>
       </c>
       <c r="C86" s="2">
-        <v>0.18454240262508392</v>
+        <v>0.18740665912628174</v>
       </c>
       <c r="D86" s="2">
         <v>-0.16843967139720917</v>
       </c>
       <c r="E86" s="2">
-        <v>-0.41696622967720032</v>
+        <v>-0.40615817904472351</v>
       </c>
     </row>
     <row r="87">
@@ -1508,13 +1508,13 @@
         <v>-1.0089346170425415</v>
       </c>
       <c r="C87" s="2">
-        <v>-1.29682457447052</v>
+        <v>-1.2886346578598022</v>
       </c>
       <c r="D87" s="2">
         <v>-0.27148890495300293</v>
       </c>
       <c r="E87" s="2">
-        <v>-0.51237577199935913</v>
+        <v>-0.50425183773040771</v>
       </c>
     </row>
     <row r="88">
@@ -1525,13 +1525,13 @@
         <v>0.6399836540222168</v>
       </c>
       <c r="C88" s="2">
-        <v>0.51158291101455688</v>
+        <v>0.51940250396728516</v>
       </c>
       <c r="D88" s="2">
         <v>-0.28811508417129517</v>
       </c>
       <c r="E88" s="2">
-        <v>-0.52213728427886963</v>
+        <v>-0.51521837711334229</v>
       </c>
     </row>
     <row r="89">
@@ -1542,13 +1542,13 @@
         <v>-0.38912945985794067</v>
       </c>
       <c r="C89" s="2">
-        <v>-0.6709216833114624</v>
+        <v>-0.66787004470825195</v>
       </c>
       <c r="D89" s="2">
         <v>-0.29760932922363281</v>
       </c>
       <c r="E89" s="2">
-        <v>-0.50987368822097778</v>
+        <v>-0.50351297855377197</v>
       </c>
     </row>
     <row r="90">
@@ -1559,13 +1559,13 @@
         <v>-0.28108114004135132</v>
       </c>
       <c r="C90" s="2">
-        <v>-0.40730690956115723</v>
+        <v>-0.39959615468978882</v>
       </c>
       <c r="D90" s="2">
         <v>-0.17618143558502197</v>
       </c>
       <c r="E90" s="2">
-        <v>-0.38886404037475586</v>
+        <v>-0.38394275307655334</v>
       </c>
     </row>
     <row r="91">
@@ -1576,13 +1576,13 @@
         <v>-0.66201239824295044</v>
       </c>
       <c r="C91" s="2">
-        <v>-0.78585058450698853</v>
+        <v>-0.78370869159698486</v>
       </c>
       <c r="D91" s="2">
         <v>-0.27070972323417664</v>
       </c>
       <c r="E91" s="2">
-        <v>-0.47794094681739807</v>
+        <v>-0.47282141447067261</v>
       </c>
     </row>
     <row r="92">
@@ -1593,13 +1593,13 @@
         <v>-0.63388866186141968</v>
       </c>
       <c r="C92" s="2">
-        <v>-0.84441655874252319</v>
+        <v>-0.84522861242294312</v>
       </c>
       <c r="D92" s="2">
         <v>-0.19565790891647339</v>
       </c>
       <c r="E92" s="2">
-        <v>-0.40221309661865234</v>
+        <v>-0.39706158638000488</v>
       </c>
     </row>
     <row r="93">
@@ -1610,13 +1610,13 @@
         <v>-0.44194155931472778</v>
       </c>
       <c r="C93" s="2">
-        <v>-0.69648629426956177</v>
+        <v>-0.69035619497299194</v>
       </c>
       <c r="D93" s="2">
         <v>-0.30421113967895508</v>
       </c>
       <c r="E93" s="2">
-        <v>-0.51340466737747192</v>
+        <v>-0.5086401104927063</v>
       </c>
     </row>
     <row r="94">
@@ -1627,13 +1627,13 @@
         <v>0.80322116613388062</v>
       </c>
       <c r="C94" s="2">
-        <v>0.5059049129486084</v>
+        <v>0.51310044527053833</v>
       </c>
       <c r="D94" s="2">
         <v>-0.21648773550987244</v>
       </c>
       <c r="E94" s="2">
-        <v>-0.40818428993225098</v>
+        <v>-0.40236014127731323</v>
       </c>
     </row>
     <row r="95">
@@ -1644,13 +1644,13 @@
         <v>-0.46260461211204529</v>
       </c>
       <c r="C95" s="2">
-        <v>-0.61714965105056763</v>
+        <v>-0.61250144243240356</v>
       </c>
       <c r="D95" s="2">
         <v>-0.15596693754196167</v>
       </c>
       <c r="E95" s="2">
-        <v>-0.37237659096717834</v>
+        <v>-0.36797401309013367</v>
       </c>
     </row>
     <row r="96">
@@ -1661,13 +1661,13 @@
         <v>-0.33346819877624512</v>
       </c>
       <c r="C96" s="2">
-        <v>-0.61527413129806519</v>
+        <v>-0.6067960262298584</v>
       </c>
       <c r="D96" s="2">
         <v>-0.12752220034599304</v>
       </c>
       <c r="E96" s="2">
-        <v>-0.34803834557533264</v>
+        <v>-0.34326177835464478</v>
       </c>
     </row>
     <row r="97">
@@ -1678,13 +1678,13 @@
         <v>-0.33699530363082886</v>
       </c>
       <c r="C97" s="2">
-        <v>-0.48914134502410889</v>
+        <v>-0.48480451107025146</v>
       </c>
       <c r="D97" s="2">
         <v>-0.055713094770908356</v>
       </c>
       <c r="E97" s="2">
-        <v>-0.29109188914299011</v>
+        <v>-0.28571736812591553</v>
       </c>
     </row>
     <row r="98">
@@ -1695,13 +1695,13 @@
         <v>0.40038111805915833</v>
       </c>
       <c r="C98" s="2">
-        <v>0.27606201171875</v>
+        <v>0.28864985704421997</v>
       </c>
       <c r="D98" s="2">
         <v>-0.074422493577003479</v>
       </c>
       <c r="E98" s="2">
-        <v>-0.3238348662853241</v>
+        <v>-0.31832563877105713</v>
       </c>
     </row>
     <row r="99">
@@ -1712,13 +1712,13 @@
         <v>0.26360598206520081</v>
       </c>
       <c r="C99" s="2">
-        <v>-0.085037678480148315</v>
+        <v>-0.090121053159236908</v>
       </c>
       <c r="D99" s="2">
         <v>-0.15668345987796783</v>
       </c>
       <c r="E99" s="2">
-        <v>-0.39981681108474731</v>
+        <v>-0.39419093728065491</v>
       </c>
     </row>
     <row r="100">
@@ -1729,13 +1729,13 @@
         <v>-0.40600967407226562</v>
       </c>
       <c r="C100" s="2">
-        <v>-0.5668063759803772</v>
+        <v>-0.56129854917526245</v>
       </c>
       <c r="D100" s="2">
         <v>-0.18423593044281006</v>
       </c>
       <c r="E100" s="2">
-        <v>-0.45312917232513428</v>
+        <v>-0.44867780804634094</v>
       </c>
     </row>
     <row r="101">
@@ -1746,13 +1746,13 @@
         <v>0.01239322405308485</v>
       </c>
       <c r="C101" s="2">
-        <v>-0.33189836144447327</v>
+        <v>-0.32732886075973511</v>
       </c>
       <c r="D101" s="2">
         <v>-0.1804722398519516</v>
       </c>
       <c r="E101" s="2">
-        <v>-0.42950022220611572</v>
+        <v>-0.42567214369773865</v>
       </c>
     </row>
     <row r="102">
@@ -1763,13 +1763,13 @@
         <v>-0.61032617092132568</v>
       </c>
       <c r="C102" s="2">
-        <v>-0.9911731481552124</v>
+        <v>-0.98383057117462158</v>
       </c>
       <c r="D102" s="2">
         <v>-0.15176080167293549</v>
       </c>
       <c r="E102" s="2">
-        <v>-0.42217010259628296</v>
+        <v>-0.41912356019020081</v>
       </c>
     </row>
     <row r="103">
@@ -1780,13 +1780,13 @@
         <v>0.062872469425201416</v>
       </c>
       <c r="C103" s="2">
-        <v>-0.17793275415897369</v>
+        <v>-0.16968721151351929</v>
       </c>
       <c r="D103" s="2">
         <v>-0.28409120440483093</v>
       </c>
       <c r="E103" s="2">
-        <v>-0.56627559661865234</v>
+        <v>-0.56392127275466919</v>
       </c>
     </row>
     <row r="104">
@@ -1797,13 +1797,13 @@
         <v>-0.71057683229446411</v>
       </c>
       <c r="C104" s="2">
-        <v>-1.0969609022140503</v>
+        <v>-1.1028833389282227</v>
       </c>
       <c r="D104" s="2">
         <v>-0.34727656841278076</v>
       </c>
       <c r="E104" s="2">
-        <v>-0.60374987125396729</v>
+        <v>-0.60014110803604126</v>
       </c>
     </row>
     <row r="105">
@@ -1814,13 +1814,13 @@
         <v>-0.29959499835968018</v>
       </c>
       <c r="C105" s="2">
-        <v>-0.40261358022689819</v>
+        <v>-0.39974495768547058</v>
       </c>
       <c r="D105" s="2">
         <v>-0.35890316963195801</v>
       </c>
       <c r="E105" s="2">
-        <v>-0.63359355926513672</v>
+        <v>-0.62964159250259399</v>
       </c>
     </row>
     <row r="106">
@@ -1831,13 +1831,13 @@
         <v>-0.078592367470264435</v>
       </c>
       <c r="C106" s="2">
-        <v>-0.4231700599193573</v>
+        <v>-0.42586743831634521</v>
       </c>
       <c r="D106" s="2">
         <v>-0.40842324495315552</v>
       </c>
       <c r="E106" s="2">
-        <v>-0.65592330694198608</v>
+        <v>-0.65190780162811279</v>
       </c>
     </row>
     <row r="107">
@@ -1848,13 +1848,13 @@
         <v>-0.79059237241744995</v>
       </c>
       <c r="C107" s="2">
-        <v>-1.0208877325057983</v>
+        <v>-1.0145297050476074</v>
       </c>
       <c r="D107" s="2">
         <v>-0.4242800772190094</v>
       </c>
       <c r="E107" s="2">
-        <v>-0.64889562129974365</v>
+        <v>-0.64549499750137329</v>
       </c>
     </row>
     <row r="108">
@@ -1865,13 +1865,13 @@
         <v>-0.30506247282028198</v>
       </c>
       <c r="C108" s="2">
-        <v>-0.4223061203956604</v>
+        <v>-0.41609922051429749</v>
       </c>
       <c r="D108" s="2">
         <v>-0.45394784212112427</v>
       </c>
       <c r="E108" s="2">
-        <v>-0.67007315158843994</v>
+        <v>-0.66716587543487549</v>
       </c>
     </row>
     <row r="109">
@@ -1882,13 +1882,13 @@
         <v>-0.51064908504486084</v>
       </c>
       <c r="C109" s="2">
-        <v>-0.83539921045303345</v>
+        <v>-0.82680326700210571</v>
       </c>
       <c r="D109" s="2">
         <v>-0.40927863121032715</v>
       </c>
       <c r="E109" s="2">
-        <v>-0.59922152757644653</v>
+        <v>-0.59512424468994141</v>
       </c>
     </row>
     <row r="110">
@@ -1899,13 +1899,13 @@
         <v>-0.4332873523235321</v>
       </c>
       <c r="C110" s="2">
-        <v>-0.53286606073379517</v>
+        <v>-0.52772438526153564</v>
       </c>
       <c r="D110" s="2">
         <v>-0.38601383566856384</v>
       </c>
       <c r="E110" s="2">
-        <v>-0.58057320117950439</v>
+        <v>-0.5762932300567627</v>
       </c>
     </row>
     <row r="111">
@@ -1916,13 +1916,13 @@
         <v>-0.75303781032562256</v>
       </c>
       <c r="C111" s="2">
-        <v>-0.92792421579360962</v>
+        <v>-0.92611563205718994</v>
       </c>
       <c r="D111" s="2">
         <v>-0.37001535296440125</v>
       </c>
       <c r="E111" s="2">
-        <v>-0.54524475336074829</v>
+        <v>-0.54096025228500366</v>
       </c>
     </row>
     <row r="112">
@@ -1933,13 +1933,13 @@
         <v>-0.20413732528686523</v>
       </c>
       <c r="C112" s="2">
-        <v>-0.36853024363517761</v>
+        <v>-0.36472475528717041</v>
       </c>
       <c r="D112" s="2">
         <v>-0.31648710370063782</v>
       </c>
       <c r="E112" s="2">
-        <v>-0.48325872421264648</v>
+        <v>-0.47972333431243896</v>
       </c>
     </row>
     <row r="113">
@@ -1950,13 +1950,13 @@
         <v>-0.3085540235042572</v>
       </c>
       <c r="C113" s="2">
-        <v>-0.45929652452468872</v>
+        <v>-0.45450884103775024</v>
       </c>
       <c r="D113" s="2">
         <v>-0.29432645440101624</v>
       </c>
       <c r="E113" s="2">
-        <v>-0.46546670794487</v>
+        <v>-0.46193763613700867</v>
       </c>
     </row>
     <row r="114">
@@ -1967,13 +1967,13 @@
         <v>-0.090211838483810425</v>
       </c>
       <c r="C114" s="2">
-        <v>-0.23477838933467865</v>
+        <v>-0.23026604950428009</v>
       </c>
       <c r="D114" s="2">
         <v>-0.25587639212608337</v>
       </c>
       <c r="E114" s="2">
-        <v>-0.40017840266227722</v>
+        <v>-0.3969167172908783</v>
       </c>
     </row>
     <row r="115">
@@ -1984,13 +1984,13 @@
         <v>0.065394096076488495</v>
       </c>
       <c r="C115" s="2">
-        <v>-0.10521429032087326</v>
+        <v>-0.10787046700716019</v>
       </c>
       <c r="D115" s="2">
         <v>-0.25393092632293701</v>
       </c>
       <c r="E115" s="2">
-        <v>-0.40593516826629639</v>
+        <v>-0.40235611796379089</v>
       </c>
     </row>
     <row r="116">
@@ -2001,13 +2001,13 @@
         <v>-0.30883818864822388</v>
       </c>
       <c r="C116" s="2">
-        <v>-0.4630134105682373</v>
+        <v>-0.46339747309684753</v>
       </c>
       <c r="D116" s="2">
         <v>-0.24248038232326508</v>
       </c>
       <c r="E116" s="2">
-        <v>-0.38131621479988098</v>
+        <v>-0.37710949778556824</v>
       </c>
     </row>
     <row r="117">
@@ -2018,13 +2018,13 @@
         <v>-0.10561659932136536</v>
       </c>
       <c r="C117" s="2">
-        <v>-0.26217794418334961</v>
+        <v>-0.25602787733078003</v>
       </c>
       <c r="D117" s="2">
         <v>-0.27141019701957703</v>
       </c>
       <c r="E117" s="2">
-        <v>-0.41599258780479431</v>
+        <v>-0.41269731521606445</v>
       </c>
     </row>
     <row r="118">
@@ -2035,13 +2035,13 @@
         <v>-0.16459836065769196</v>
       </c>
       <c r="C118" s="2">
-        <v>-0.24780447781085968</v>
+        <v>-0.24161499738693237</v>
       </c>
       <c r="D118" s="2">
         <v>-0.26587346196174622</v>
       </c>
       <c r="E118" s="2">
-        <v>-0.40973225235939026</v>
+        <v>-0.40681672096252441</v>
       </c>
     </row>
     <row r="119">
@@ -2052,13 +2052,13 @@
         <v>-0.41577836871147156</v>
       </c>
       <c r="C119" s="2">
-        <v>-0.58467692136764526</v>
+        <v>-0.57667899131774902</v>
       </c>
       <c r="D119" s="2">
         <v>-0.31620165705680847</v>
       </c>
       <c r="E119" s="2">
-        <v>-0.45612061023712158</v>
+        <v>-0.45267710089683533</v>
       </c>
     </row>
     <row r="120">
@@ -2069,13 +2069,13 @@
         <v>-0.64998281002044678</v>
       </c>
       <c r="C120" s="2">
-        <v>-0.70635378360748291</v>
+        <v>-0.69889593124389648</v>
       </c>
       <c r="D120" s="2">
         <v>-0.40068012475967407</v>
       </c>
       <c r="E120" s="2">
-        <v>-0.536063551902771</v>
+        <v>-0.53218454122543335</v>
       </c>
     </row>
     <row r="121">
@@ -2086,13 +2086,13 @@
         <v>-0.4645056426525116</v>
       </c>
       <c r="C121" s="2">
-        <v>-0.6806175708770752</v>
+        <v>-0.68501526117324829</v>
       </c>
       <c r="D121" s="2">
         <v>-0.41660252213478088</v>
       </c>
       <c r="E121" s="2">
-        <v>-0.56016486883163452</v>
+        <v>-0.55589938163757324</v>
       </c>
     </row>
     <row r="122">
@@ -2103,13 +2103,13 @@
         <v>-0.25872346758842468</v>
       </c>
       <c r="C122" s="2">
-        <v>-0.40295359492301941</v>
+        <v>-0.40158355236053467</v>
       </c>
       <c r="D122" s="2">
         <v>-0.43111085891723633</v>
       </c>
       <c r="E122" s="2">
-        <v>-0.57732683420181274</v>
+        <v>-0.57316267490386963</v>
       </c>
     </row>
     <row r="123">
@@ -2120,13 +2120,13 @@
         <v>-0.54316568374633789</v>
       </c>
       <c r="C123" s="2">
-        <v>-0.65227353572845459</v>
+        <v>-0.6430094838142395</v>
       </c>
       <c r="D123" s="2">
         <v>-0.41099384427070618</v>
       </c>
       <c r="E123" s="2">
-        <v>-0.57443976402282715</v>
+        <v>-0.56976747512817383</v>
       </c>
     </row>
     <row r="124">
@@ -2137,13 +2137,13 @@
         <v>-0.69491207599639893</v>
       </c>
       <c r="C124" s="2">
-        <v>-0.82470059394836426</v>
+        <v>-0.8234373927116394</v>
       </c>
       <c r="D124" s="2">
         <v>-0.39766961336135864</v>
       </c>
       <c r="E124" s="2">
-        <v>-0.57073277235031128</v>
+        <v>-0.5667649507522583</v>
       </c>
     </row>
     <row r="125">
@@ -2154,13 +2154,13 @@
         <v>-0.45213967561721802</v>
       </c>
       <c r="C125" s="2">
-        <v>-0.67992526292800903</v>
+        <v>-0.67683082818984985</v>
       </c>
       <c r="D125" s="2">
         <v>-0.36088427901268005</v>
       </c>
       <c r="E125" s="2">
-        <v>-0.55864185094833374</v>
+        <v>-0.55396956205368042</v>
       </c>
     </row>
     <row r="126">
@@ -2171,13 +2171,13 @@
         <v>-0.236191526055336</v>
       </c>
       <c r="C126" s="2">
-        <v>-0.416635662317276</v>
+        <v>-0.41139787435531616</v>
       </c>
       <c r="D126" s="2">
         <v>-0.42693674564361572</v>
       </c>
       <c r="E126" s="2">
-        <v>-0.63127231597900391</v>
+        <v>-0.62580627202987671</v>
       </c>
     </row>
     <row r="127">
@@ -2188,13 +2188,13 @@
         <v>0.01645464263856411</v>
       </c>
       <c r="C127" s="2">
-        <v>-0.22182111442089081</v>
+        <v>-0.21105813980102539</v>
       </c>
       <c r="D127" s="2">
         <v>-0.3439827561378479</v>
       </c>
       <c r="E127" s="2">
-        <v>-0.54706573486328125</v>
+        <v>-0.54047310352325439</v>
       </c>
     </row>
     <row r="128">
@@ -2205,13 +2205,13 @@
         <v>-0.29586023092269897</v>
       </c>
       <c r="C128" s="2">
-        <v>-0.55131393671035767</v>
+        <v>-0.5496559739112854</v>
       </c>
       <c r="D128" s="2">
         <v>-0.31330099701881409</v>
       </c>
       <c r="E128" s="2">
-        <v>-0.52649039030075073</v>
+        <v>-0.52068918943405151</v>
       </c>
     </row>
     <row r="129">
@@ -2222,13 +2222,13 @@
         <v>-0.3189147412776947</v>
       </c>
       <c r="C129" s="2">
-        <v>-0.59753537178039551</v>
+        <v>-0.58373761177062988</v>
       </c>
       <c r="D129" s="2">
         <v>-0.19910748302936554</v>
       </c>
       <c r="E129" s="2">
-        <v>-0.41502860188484192</v>
+        <v>-0.40902939438819885</v>
       </c>
     </row>
     <row r="130">
@@ -2239,13 +2239,13 @@
         <v>-1.0589779615402222</v>
       </c>
       <c r="C130" s="2">
-        <v>-1.334291934967041</v>
+        <v>-1.3315454721450806</v>
       </c>
       <c r="D130" s="2">
         <v>-0.13768768310546875</v>
       </c>
       <c r="E130" s="2">
-        <v>-0.34944146871566772</v>
+        <v>-0.34175559878349304</v>
       </c>
     </row>
     <row r="131">
@@ -2256,13 +2256,13 @@
         <v>0.48786237835884094</v>
       </c>
       <c r="C131" s="2">
-        <v>0.35490584373474121</v>
+        <v>0.36641496419906616</v>
       </c>
       <c r="D131" s="2">
         <v>-0.16731062531471252</v>
       </c>
       <c r="E131" s="2">
-        <v>-0.37694743275642395</v>
+        <v>-0.36859589815139771</v>
       </c>
     </row>
     <row r="132">
@@ -2273,13 +2273,13 @@
         <v>-0.26702976226806641</v>
       </c>
       <c r="C132" s="2">
-        <v>-0.46709522604942322</v>
+        <v>-0.46495422720909119</v>
       </c>
       <c r="D132" s="2">
         <v>-0.15201237797737122</v>
       </c>
       <c r="E132" s="2">
-        <v>-0.36996603012084961</v>
+        <v>-0.3628697395324707</v>
       </c>
     </row>
     <row r="133">
@@ -2290,13 +2290,13 @@
         <v>0.33282959461212158</v>
       </c>
       <c r="C133" s="2">
-        <v>0.17845536768436432</v>
+        <v>0.18150065839290619</v>
       </c>
       <c r="D133" s="2">
         <v>-0.10918814688920975</v>
       </c>
       <c r="E133" s="2">
-        <v>-0.32089641690254211</v>
+        <v>-0.31281039118766785</v>
       </c>
     </row>
     <row r="134">
@@ -2307,13 +2307,13 @@
         <v>0.10063840448856354</v>
       </c>
       <c r="C134" s="2">
-        <v>-0.089641056954860687</v>
+        <v>-0.071366764605045319</v>
       </c>
       <c r="D134" s="2">
         <v>-0.14214363694190979</v>
       </c>
       <c r="E134" s="2">
-        <v>-0.34276983141899109</v>
+        <v>-0.33584710955619812</v>
       </c>
     </row>
     <row r="135">
@@ -2324,13 +2324,13 @@
         <v>-0.50279790163040161</v>
       </c>
       <c r="C135" s="2">
-        <v>-0.66418945789337158</v>
+        <v>-0.65296047925949097</v>
       </c>
       <c r="D135" s="2">
         <v>0.01849055290222168</v>
       </c>
       <c r="E135" s="2">
-        <v>-0.16546542942523956</v>
+        <v>-0.15789970755577087</v>
       </c>
     </row>
     <row r="136">
@@ -2341,13 +2341,13 @@
         <v>0.15413878858089447</v>
       </c>
       <c r="C136" s="2">
-        <v>-0.15898846089839935</v>
+        <v>-0.15952268242835999</v>
       </c>
       <c r="D136" s="2">
         <v>0.0097830193117260933</v>
       </c>
       <c r="E136" s="2">
-        <v>-0.17856661975383759</v>
+        <v>-0.17164860665798187</v>
       </c>
     </row>
     <row r="137">
@@ -2358,13 +2358,13 @@
         <v>0.089557856321334839</v>
       </c>
       <c r="C137" s="2">
-        <v>-0.10968752950429916</v>
+        <v>-0.099121928215026855</v>
       </c>
       <c r="D137" s="2">
-        <v>0.044384617358446121</v>
+        <v>-0.0062505933456122875</v>
       </c>
       <c r="E137" s="2">
-        <v>-0.14250054955482483</v>
+        <v>-0.17746853828430176</v>
       </c>
     </row>
     <row r="138">
@@ -2375,13 +2375,13 @@
         <v>-0.61551415920257568</v>
       </c>
       <c r="C138" s="2">
-        <v>-0.79439610242843628</v>
+        <v>-0.79106795787811279</v>
       </c>
       <c r="D138" s="2">
-        <v>0.0031781920697540045</v>
+        <v>-0.038646884262561798</v>
       </c>
       <c r="E138" s="2">
-        <v>-0.18835139274597168</v>
+        <v>-0.22276662290096283</v>
       </c>
     </row>
     <row r="139">
@@ -2392,13 +2392,13 @@
         <v>0.38672977685928345</v>
       </c>
       <c r="C139" s="2">
-        <v>0.26144778728485107</v>
+        <v>0.26998099684715271</v>
       </c>
       <c r="D139" s="2">
-        <v>-0.013065177015960217</v>
+        <v>-0.025841487571597099</v>
       </c>
       <c r="E139" s="2">
-        <v>-0.20480312407016754</v>
+        <v>-0.21901942789554596</v>
       </c>
     </row>
     <row r="140">
@@ -2409,95 +2409,239 @@
         <v>0.40949457883834839</v>
       </c>
       <c r="C140" s="2">
-        <v>0.23699504137039185</v>
+        <v>0.24267487227916718</v>
       </c>
       <c r="D140" s="2">
-        <v>0.084881365299224854</v>
+        <v>-0.010508239269256592</v>
       </c>
       <c r="E140" s="2">
-        <v>-0.11292584985494614</v>
+        <v>-0.21266643702983856</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1">
         <v>45505</v>
       </c>
-      <c r="B141" s="2"/>
-      <c r="C141" s="2"/>
-      <c r="D141" s="2"/>
-      <c r="E141" s="2"/>
+      <c r="B141" s="2">
+        <v>-0.41133227944374084</v>
+      </c>
+      <c r="C141" s="2">
+        <v>-0.5173335075378418</v>
+      </c>
+      <c r="D141" s="2">
+        <v>-0.12890252470970154</v>
+      </c>
+      <c r="E141" s="2">
+        <v>-0.3198414146900177</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1">
         <v>45536</v>
       </c>
-      <c r="B142" s="2"/>
-      <c r="C142" s="2"/>
-      <c r="D142" s="2"/>
-      <c r="E142" s="2"/>
+      <c r="B142" s="2">
+        <v>0.041262973099946976</v>
+      </c>
+      <c r="C142" s="2">
+        <v>-0.22618210315704346</v>
+      </c>
+      <c r="D142" s="2">
+        <v>-0.1748775839805603</v>
+      </c>
+      <c r="E142" s="2">
+        <v>-0.36524909734725952</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1">
         <v>45566</v>
       </c>
-      <c r="B143" s="2"/>
-      <c r="C143" s="2"/>
-      <c r="D143" s="2"/>
-      <c r="E143" s="2"/>
+      <c r="B143" s="2">
+        <v>0.21588698029518127</v>
+      </c>
+      <c r="C143" s="2">
+        <v>-0.037642121315002441</v>
+      </c>
+      <c r="D143" s="2">
+        <v>-0.18485830724239349</v>
+      </c>
+      <c r="E143" s="2">
+        <v>-0.37300807237625122</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1">
         <v>45597</v>
       </c>
-      <c r="B144" s="2"/>
-      <c r="C144" s="2"/>
-      <c r="D144" s="2"/>
-      <c r="E144" s="2"/>
+      <c r="B144" s="2">
+        <v>-0.36479866504669189</v>
+      </c>
+      <c r="C144" s="2">
+        <v>-0.59578347206115723</v>
+      </c>
+      <c r="D144" s="2">
+        <v>-0.23691539466381073</v>
+      </c>
+      <c r="E144" s="2">
+        <v>-0.43123361468315125</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1">
         <v>45627</v>
       </c>
-      <c r="B145" s="2"/>
-      <c r="C145" s="2"/>
-      <c r="D145" s="2"/>
-      <c r="E145" s="2"/>
+      <c r="B145" s="2">
+        <v>-0.91140979528427124</v>
+      </c>
+      <c r="C145" s="2">
+        <v>-1.124097466468811</v>
+      </c>
+      <c r="D145" s="2">
+        <v>-0.36118766665458679</v>
+      </c>
+      <c r="E145" s="2">
+        <v>-0.54746663570404053</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1">
         <v>45658</v>
       </c>
-      <c r="B146" s="2"/>
-      <c r="C146" s="2"/>
-      <c r="D146" s="2"/>
-      <c r="E146" s="2"/>
+      <c r="B146" s="2">
+        <v>-0.32421761751174927</v>
+      </c>
+      <c r="C146" s="2">
+        <v>-0.50779122114181519</v>
+      </c>
+      <c r="D146" s="2">
+        <v>-0.35491958260536194</v>
+      </c>
+      <c r="E146" s="2">
+        <v>-0.55123323202133179</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1">
         <v>45689</v>
       </c>
-      <c r="B147" s="2"/>
-      <c r="C147" s="2"/>
-      <c r="D147" s="2"/>
-      <c r="E147" s="2"/>
+      <c r="B147" s="2">
+        <v>-0.70534074306488037</v>
+      </c>
+      <c r="C147" s="2">
+        <v>-0.86089861392974854</v>
+      </c>
+      <c r="D147" s="2">
+        <v>-0.41151711344718933</v>
+      </c>
+      <c r="E147" s="2">
+        <v>-0.59766912460327148</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1">
         <v>45717</v>
       </c>
-      <c r="B148" s="2"/>
-      <c r="C148" s="2"/>
-      <c r="D148" s="2"/>
-      <c r="E148" s="2"/>
+      <c r="B148" s="2">
+        <v>-0.081783987581729889</v>
+      </c>
+      <c r="C148" s="2">
+        <v>-0.25404897332191467</v>
+      </c>
+      <c r="D148" s="2">
+        <v>-0.51608443260192871</v>
+      </c>
+      <c r="E148" s="2">
+        <v>-0.69100695848464966</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1">
         <v>45748</v>
       </c>
-      <c r="B149" s="2"/>
-      <c r="C149" s="2"/>
-      <c r="D149" s="2"/>
-      <c r="E149" s="2"/>
+      <c r="B149" s="2">
+        <v>-0.70895588397979736</v>
+      </c>
+      <c r="C149" s="2">
+        <v>-0.80342203378677368</v>
+      </c>
+      <c r="D149" s="2">
+        <v>-0.54634159803390503</v>
+      </c>
+      <c r="E149" s="2">
+        <v>-0.71005165576934814</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+      <c r="E151" s="2"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="1">
+        <v>45839</v>
+      </c>
+      <c r="B152" s="2"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
+      <c r="E152" s="2"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="2"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
+      <c r="E154" s="2"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B155" s="2"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
+      <c r="E155" s="2"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
+      <c r="E156" s="2"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
+      <c r="E157" s="2"/>
     </row>
   </sheetData>
 </worksheet>
